--- a/data/products_docs/product_dress.xlsx
+++ b/data/products_docs/product_dress.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29108"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2716C62-E107-4F4A-8C27-4A4FF698C3CB}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E25A4BE-9B03-42BF-8AC9-6B6AFD7CDB84}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>id</t>
   </si>
@@ -45,7 +45,10 @@
     <t>description</t>
   </si>
   <si>
-    <t>item004</t>
+    <t>price</t>
+  </si>
+  <si>
+    <t>item206</t>
   </si>
   <si>
     <t>サマーワンピース</t>
@@ -435,10 +438,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -451,19 +454,25 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75">
+    <row r="2" spans="1:5" ht="15.75">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>3990</v>
       </c>
     </row>
   </sheetData>
